--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707426-115-CM26</t>
+          <t>3950-3939-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2427.43</v>
+        <v>795.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2151-314-CM26</t>
+          <t>2713-634-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>844.95</v>
+        <v>3616.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1692-563-CM26</t>
+          <t>2713-635-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1182.38</v>
+        <v>1684.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2500-127-CM26</t>
+          <t>951405-242-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>807.59</v>
+        <v>3773.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2500-126-CM26</t>
+          <t>1003-154-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3960.16</v>
+        <v>1027.18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2500-129-CM26</t>
+          <t>1252675-67-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1652.06</v>
+        <v>923.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3951-231-CM26</t>
+          <t>951405-287-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8074.89</v>
+        <v>1855.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>886182-275-CM26</t>
+          <t>2713-824-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,6 +996,860 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>2064.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1691-2345-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RED OFFICE SUR LTDA.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>8149.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>734-898-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3177.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1746-228-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ANTALIS CHILE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.305.910-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2151-354-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>1215.93</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>707426-159-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>2491.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>854-332-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1452.94</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>707426-115-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>2427.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2151-314-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.955.038-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>844.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1692-563-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1182.38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2500-127-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>807.59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2500-126-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>3960.16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2500-129-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1652.06</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3951-231-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.974.700-3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>8074.89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>886182-275-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>7443.42</v>
       </c>
     </row>
